--- a/outputs/tco_analysis.xlsx
+++ b/outputs/tco_analysis.xlsx
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36416.14</v>
+        <v>38255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37889.58</v>
+        <v>41812.71</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39422.63</v>
+        <v>45701.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41017.72</v>
+        <v>49951.52</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42677.34</v>
+        <v>54597.01</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44404.12</v>
+        <v>59674.53</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>46200.76</v>
+        <v>65224.26</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48070.09</v>
+        <v>71290.12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50015.07</v>
+        <v>77920.10000000001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>52038.73</v>
+        <v>85166.67</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>938152.1899999999</v>
+        <v>1089593.22</v>
       </c>
     </row>
   </sheetData>
